--- a/data/trans_orig/IP16A10-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16A10-Estudios-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>3337</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17058</t>
+          <t>17025</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38826</t>
+          <t>38968</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8762</t>
+          <t>8651</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11422</t>
+          <t>11614</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71945</t>
+          <t>72056</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78332</t>
+          <t>78402</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>83360</t>
+          <t>82812</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>156954</t>
+          <t>156762</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>165026</t>
+          <t>165025</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>510</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4342</t>
+          <t>4518</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>619</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5760</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18209</t>
+          <t>18033</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22040</t>
+          <t>22041</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31823</t>
+          <t>31578</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52056</t>
+          <t>52300</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>57204</t>
+          <t>57197</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3459</t>
+          <t>3573</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11637</t>
+          <t>11072</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>722</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6984</t>
+          <t>6786</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15658</t>
+          <t>15209</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>113668</t>
+          <t>114233</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>121846</t>
+          <t>121732</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>136209</t>
+          <t>136407</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>142523</t>
+          <t>142471</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>252840</t>
+          <t>253289</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>262700</t>
+          <t>262621</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19677</t>
+          <t>19793</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45819</t>
+          <t>45273</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>500</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4592</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>8862</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>9594</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>111017</t>
+          <t>110464</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>115609</t>
+          <t>115109</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>114563</t>
+          <t>113904</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>121461</t>
+          <t>121453</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>228330</t>
+          <t>228781</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>235855</t>
+          <t>235945</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>5132</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5577</t>
+          <t>5709</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40583</t>
+          <t>40727</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85514</t>
+          <t>85382</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7525</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>8057</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13254</t>
+          <t>13004</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>179467</t>
+          <t>179747</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>185869</t>
+          <t>185799</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>182150</t>
+          <t>182793</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>188975</t>
+          <t>189536</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>364588</t>
+          <t>364838</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>374175</t>
+          <t>374039</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5895</t>
+          <t>6560</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>101814</t>
+          <t>102282</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>92853</t>
+          <t>92865</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>197706</t>
+          <t>197041</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>3290</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34006</t>
+          <t>34480</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34747</t>
+          <t>34494</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>71153</t>
+          <t>71511</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>557</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4794</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5451</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7953</t>
+          <t>7846</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>157880</t>
+          <t>157742</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>161978</t>
+          <t>161979</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>142674</t>
+          <t>142507</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>147466</t>
+          <t>147469</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>302708</t>
+          <t>302815</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>309312</t>
+          <t>309268</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A10-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16A10-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3277</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>16,18%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3233</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3598</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>15,96%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3337</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19616</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16981</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,83%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>83,82%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>19616</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>17025</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,83%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>84,04%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>62</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38968</t>
+          <t>38707</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1392</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4836</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>5136</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2305</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8651</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2532</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9081</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>6,36%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,72%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1392</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4857</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11614</t>
+          <t>11718</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>86277</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>82833</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,41%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,48%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>75571</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>72056</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>78402</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>71626</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>78175</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>93,64%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>89,28%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,14%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>86277</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>82812</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,41%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>156762</t>
+          <t>156658</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>165025</t>
+          <t>164810</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3446</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,77%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1661</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4518</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4170</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>7,36%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20,03%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3688</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5516</t>
+          <t>5734</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>34581</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>31820</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,06%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,23%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>20890</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>18033</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>22041</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>18381</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>22051</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>92,64%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>79,97%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,74%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>34581</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>31578</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,06%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52300</t>
+          <t>52082</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,28%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>6797</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3573</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11072</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3809</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11888</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,42%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,84%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2719</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>722</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6786</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15209</t>
+          <t>14734</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>140474</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>137060</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>142516</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,1%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,72%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,53%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>118508</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>114233</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>121732</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>113417</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>121496</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,58%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,16%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,15%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>140474</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>136407</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>142471</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,1%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>253289</t>
+          <t>253764</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>262621</t>
+          <t>263064</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2325,107 +2325,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2792</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,22%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>607</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3059</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3163</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>13,39%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3102</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -2438,74 +2438,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>22245</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>20060</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22852</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,34%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,78%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>25523</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>22245</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>19793</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22852</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,34%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>86,61%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>68</t>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45273</t>
+          <t>45212</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>22852</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>22852</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>22852</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>25523</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>25523</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>25523</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>22852</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>22852</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>22852</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2668,72 +2668,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3490</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1290</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8020</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,84%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,53%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1708</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5145</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4635</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,48%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3490</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1313</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8862</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>10090</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -2781,74 +2781,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>119276</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>114746</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>121476</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,16%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,47%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,95%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>113901</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>110464</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>115109</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>110974</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>115116</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,52%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,55%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>95,99%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,57%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>119276</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>113904</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>121453</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,16%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>92,78%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>98,93%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>335</t>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>228781</t>
+          <t>228285</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>235945</t>
+          <t>235990</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>122766</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>122766</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>122766</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>115609</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>115609</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>115609</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>122766</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>122766</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>122766</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3011,107 +3011,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1589</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5132</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,46%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,19%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>11,49%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1589</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5112</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1589</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5709</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -3124,74 +3124,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>45232</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>44270</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>40727</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>40590</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>45859</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,54%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>88,81%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>88,51%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>45232</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>125</t>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85382</t>
+          <t>85979</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>45232</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>45232</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>45232</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>45859</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>45859</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>45859</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>45232</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>45232</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>45232</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3354,72 +3354,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4097</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1547</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8784</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3296</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1193</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7245</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1211</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7613</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,76%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4097</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1314</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8057</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13004</t>
+          <t>12980</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3472,67 +3472,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>186753</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>182066</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>189303</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,85%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,4%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>183696</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>179747</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>185799</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>179379</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>185781</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,24%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,13%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>186753</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>182793</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>189536</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>364838</t>
+          <t>364862</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>374039</t>
+          <t>373927</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>190850</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>190850</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>190850</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>186992</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>190850</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>190850</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>190850</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4041,47 +4041,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12775</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18856</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12775</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4154,57 +4154,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12775</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12775</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12775</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>18856</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>18856</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>18856</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>12775</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>12775</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>12775</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4276,67 +4276,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,41%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>1173</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3628</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4212</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,11%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,43%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1399</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4827</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>695</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6560</t>
+          <t>6632</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -4384,74 +4384,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>96293</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>93387</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>97692</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,57%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,59%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>104737</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>102282</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>101698</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>105910</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,89%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,57%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,02%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>96293</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>92865</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>97692</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,57%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>95,06%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>301</t>
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>197041</t>
+          <t>196969</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>202901</t>
+          <t>202906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>97692</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>97692</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>97692</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>105910</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>105910</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>105910</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>97692</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>97692</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>97692</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4619,102 +4619,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3295</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,75%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>589</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3290</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3038</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,56%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>663</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1252</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3165</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4007</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>8,4%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1252</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3918</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -4727,74 +4727,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>36996</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>34364</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>37659</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,24%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,25%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>37181</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>34480</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>34732</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>37770</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,44%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>91,29%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>91,96%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>36996</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>34494</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>37659</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,24%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>91,6%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>108</t>
@@ -4807,7 +4807,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>71511</t>
+          <t>71422</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4840,57 +4840,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>37659</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>37659</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>37659</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>37770</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>37770</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>37770</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>37659</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>37659</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>37659</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4962,67 +4962,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4881</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>1762</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>557</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4794</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4830</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,08%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2062</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5618</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7846</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -5070,74 +5070,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>146063</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>143244</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>147464</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,61%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,7%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>160774</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>157742</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>161979</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>157706</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>161982</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,92%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,05%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,03%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,66%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>146063</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>142507</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>147469</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>96,21%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>454</t>
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>302815</t>
+          <t>302713</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>309268</t>
+          <t>309269</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>162536</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
